--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104625_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104625_W19.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.681</v>
+        <v>5.8123</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0238</v>
+        <v>6.8271</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3428</v>
+        <v>-1.0148</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6986</v>
+        <v>-0.7402</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0717</v>
+        <v>-1.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3731</v>
+        <v>0.3583</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3192</v>
+        <v>4.2434</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0786</v>
+        <v>0.0368</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2406</v>
+        <v>4.2067</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.0178</v>
+        <v>-4.9836</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.8675</v>
+        <v>-3.8483</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>4.083</v>
+        <v>4.0974</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4201</v>
+        <v>0.7605</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0121</v>
+        <v>0.8891</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.408</v>
+        <v>-0.1286</v>
       </c>
       <c r="V2" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6267</v>
+        <v>1.9719</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3574</v>
+        <v>1.849</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2693</v>
+        <v>0.1229</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1935</v>
+        <v>-0.2053</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5284</v>
+        <v>1.5089</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7219</v>
+        <v>-1.7142</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2571</v>
+        <v>3.2179</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6628</v>
+        <v>2.6298</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4506</v>
+        <v>-3.4232</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.3162</v>
+        <v>-2.3023</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S3" t="n">
-        <v>3.979</v>
+        <v>2.3365</v>
       </c>
       <c r="T3" t="n">
-        <v>3.342</v>
+        <v>1.8878</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6369</v>
+        <v>0.4487</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6028</v>
+        <v>1.6215</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4545</v>
+        <v>1.5043</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8517</v>
+        <v>0.1172</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4567</v>
+        <v>0.962</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1848</v>
+        <v>1.4102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2719</v>
+        <v>-0.4482</v>
       </c>
       <c r="J4" t="n">
-        <v>3.157</v>
+        <v>2.3642</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0824</v>
+        <v>1.9995</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.3647</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7003</v>
+        <v>-1.4022</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8976</v>
+        <v>-0.5893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1973</v>
+        <v>-0.8129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>3.29</v>
+        <v>-0.251</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8853</v>
+        <v>0.2783</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4047</v>
+        <v>-0.5294</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.8243</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.3707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0571</v>
+        <v>0.9062</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2148</v>
+        <v>3.9774</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1577</v>
+        <v>-3.0712</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9567</v>
+        <v>2.4547</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4098</v>
+        <v>2.1774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4531</v>
+        <v>0.2773</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3792</v>
+        <v>3.1426</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0087</v>
+        <v>3.0682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3705</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4225</v>
+        <v>-0.6879</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.599</v>
+        <v>-0.8907</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8236</v>
+        <v>0.2028</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8069</v>
+        <v>1.5817</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0302</v>
+        <v>1.4282</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7766999999999999</v>
+        <v>0.1535</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-3.8132</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1794</v>
+        <v>-0.2444</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0094</v>
+        <v>-0.895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.83</v>
+        <v>0.6506</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3143</v>
+        <v>-0.3095</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1357</v>
+        <v>-0.1323</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1066</v>
+        <v>0.1062</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5886</v>
+        <v>0.5203</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0181</v>
+        <v>0.137</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5704</v>
+        <v>0.3834</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9272</v>
+        <v>-0.7755</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.712</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0047</v>
+        <v>-0.0635</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0204</v>
+        <v>-2.0121</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7059</v>
+        <v>-1.6962</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7885</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L7" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8089</v>
+        <v>-2.7918</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4149</v>
+        <v>-2.4037</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4286</v>
+        <v>-0.287</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3185</v>
+        <v>0.2243</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6276</v>
+        <v>-1.7355</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3001</v>
+        <v>-0.2197</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3275</v>
+        <v>-1.5158</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3287</v>
+        <v>-4.978</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7849</v>
+        <v>-1.2094</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5437</v>
+        <v>-3.7686</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1347</v>
+        <v>-1.4691</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.769</v>
+        <v>-0.6345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6344</v>
+        <v>-0.8345</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.194</v>
+        <v>-3.5089</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0159</v>
+        <v>-0.5749</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1781</v>
+        <v>-2.934</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1155</v>
+        <v>0.3319</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4869</v>
+        <v>0.1599</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3714</v>
+        <v>0.1721</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8639</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6847</v>
+        <v>-2.5197</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2685</v>
+        <v>0.0436</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4161</v>
+        <v>-2.5632</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9853</v>
+        <v>-1.3274</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2136</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.7717</v>
+        <v>-0.5406</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4569</v>
+        <v>-0.1394</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.7724</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8264</v>
+        <v>0.633</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5284</v>
+        <v>-1.1881</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5831</v>
+        <v>-0.0144</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.9453</v>
+        <v>-1.1736</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6067</v>
+        <v>-0.0117</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9043</v>
+        <v>-0.1326</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2976</v>
+        <v>0.1209</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>-1.8634</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8376</v>
+        <v>-3.8278</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6727</v>
+        <v>-1.5341</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1649</v>
+        <v>-2.2936</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3145</v>
+        <v>-2.8682</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.307</v>
+        <v>0.1095</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0076</v>
+        <v>-2.9776</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.207</v>
+        <v>-0.0054</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7716</v>
+        <v>0.1961</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5646</v>
+        <v>-0.2015</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1075</v>
+        <v>-2.8628</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5354</v>
+        <v>-0.0866</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5721</v>
+        <v>-2.7761</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4374</v>
+        <v>0.7932</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6684</v>
+        <v>0.6385</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2311</v>
+        <v>0.1546</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4141</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4141</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9284</v>
+        <v>-4.8732</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3207</v>
+        <v>-3.8624</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6077</v>
+        <v>-1.0108</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8645</v>
+        <v>-4.1215</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1155</v>
+        <v>-1.7088</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.98</v>
+        <v>-2.4127</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0189</v>
+        <v>-1.3442</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2109</v>
+        <v>-1.4931</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.192</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8834</v>
+        <v>-2.7774</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0954</v>
+        <v>-0.2157</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.788</v>
+        <v>-2.5617</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3173</v>
+        <v>-0.4542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1905</v>
+        <v>-0.3997</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1267</v>
+        <v>-0.0545</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0322</v>
+        <v>-5.2362</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8437</v>
+        <v>-2.2246</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1885</v>
+        <v>-3.0115</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1299</v>
+        <v>-4.3303</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.707</v>
+        <v>-3.3249</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4229</v>
+        <v>-1.0054</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3369</v>
+        <v>-1.2371</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4861</v>
+        <v>-2.7933</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1493</v>
+        <v>1.5563</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.793</v>
+        <v>-3.0932</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2209</v>
+        <v>-0.5315</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.5721</v>
+        <v>-2.5617</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6094000000000001</v>
+        <v>0.0439</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3992</v>
+        <v>0.1506</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2102</v>
+        <v>-0.1067</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1607</v>
+        <v>-1.405</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.249499999999999</v>
+        <v>-8.900400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>4.703399999999998</v>
+        <v>4.7536</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.9529</v>
+        <v>-13.6537</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.4363</v>
+        <v>-17.4758</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.2959</v>
+        <v>-3.3706</v>
       </c>
       <c r="I13" t="n">
-        <v>-14.1404</v>
+        <v>-14.1051</v>
       </c>
       <c r="J13" t="n">
-        <v>9.891</v>
+        <v>9.658799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>2.535</v>
+        <v>2.378200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>7.356299999999999</v>
+        <v>7.2809</v>
       </c>
       <c r="M13" t="n">
-        <v>-27.3273</v>
+        <v>-27.1348</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.831</v>
+        <v>-5.7486</v>
       </c>
       <c r="O13" t="n">
-        <v>-21.4964</v>
+        <v>-21.3859</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6708</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0126</v>
+        <v>-17.0726</v>
       </c>
       <c r="R13" t="n">
-        <v>22.6834</v>
+        <v>22.7633</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9905</v>
+        <v>5.364099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.143600000000001</v>
+        <v>4.525799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8468</v>
+        <v>0.8382999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4743</v>
+        <v>-2.4796</v>
       </c>
       <c r="W13" t="n">
-        <v>7.681</v>
+        <v>7.6412</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.1554</v>
+        <v>-10.1207</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6251</v>
+        <v>4.0809</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7418</v>
+        <v>1.9417</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8832</v>
+        <v>2.1392</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3779</v>
+        <v>3.3869</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2152</v>
+        <v>-0.2045</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5931</v>
+        <v>3.5914</v>
       </c>
       <c r="J14" t="n">
-        <v>2.345</v>
+        <v>2.3228</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6485</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9826</v>
+        <v>2.9713</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0329</v>
+        <v>1.0641</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3238</v>
+        <v>-0.8719</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5202</v>
+        <v>-0.2837</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8036</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4114</v>
+        <v>3.8029</v>
       </c>
       <c r="E15" t="n">
-        <v>3.418</v>
+        <v>4.7427</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0066</v>
+        <v>-0.9398</v>
       </c>
       <c r="G15" t="n">
-        <v>4.185</v>
+        <v>5.4193</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6132</v>
+        <v>0.8814</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5718</v>
+        <v>4.5379</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4053</v>
+        <v>7.8556</v>
       </c>
       <c r="K15" t="n">
-        <v>0.599</v>
+        <v>1.3994</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8063</v>
+        <v>6.4562</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2203</v>
+        <v>-2.4364</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0142</v>
+        <v>-0.518</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2345</v>
+        <v>-1.9184</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4952</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5132</v>
+        <v>0.5413</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4567</v>
+        <v>0.3714</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0565</v>
+        <v>0.1699</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2083</v>
+        <v>-0.1089</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.977</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1337</v>
+        <v>2.9523</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3264</v>
+        <v>3.1471</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1927</v>
+        <v>-0.1947</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4363</v>
+        <v>4.1894</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8758</v>
+        <v>0.6173</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5605</v>
+        <v>3.5721</v>
       </c>
       <c r="J16" t="n">
-        <v>7.8979</v>
+        <v>4.3875</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4129</v>
+        <v>0.5893</v>
       </c>
       <c r="L16" t="n">
-        <v>6.485</v>
+        <v>3.7982</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4615</v>
+        <v>-0.1981</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5371</v>
+        <v>0.028</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9245</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0415</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1518</v>
+        <v>0.0572</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1028</v>
+        <v>0.2228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.049</v>
+        <v>-0.1656</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1093</v>
+        <v>1.2097</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.27</v>
+        <v>-0.9692</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1838</v>
+        <v>1.5801</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3761</v>
+        <v>1.5297</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1923</v>
+        <v>0.0505</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0179</v>
+        <v>0.5127</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8602</v>
+        <v>0.8581</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8423</v>
+        <v>-0.3454</v>
       </c>
       <c r="J17" t="n">
-        <v>2.345</v>
+        <v>1.8596</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1487</v>
+        <v>1.1893</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1963</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3629</v>
+        <v>-1.3469</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0089</v>
+        <v>-0.3312</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.354</v>
+        <v>-1.0157</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6129</v>
+        <v>-0.705</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6079</v>
+        <v>-0.2812</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.005</v>
+        <v>-0.4237</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9167999999999999</v>
+        <v>1.5604</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4258</v>
+        <v>3.4666</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.509</v>
+        <v>-1.9062</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4977</v>
+        <v>-0.0122</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8468</v>
+        <v>-0.8507</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3492</v>
+        <v>0.8385</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8666</v>
+        <v>2.3228</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1949</v>
+        <v>0.1411</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6717</v>
+        <v>2.1816</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3689</v>
+        <v>-2.335</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.348</v>
+        <v>-0.9918</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0209</v>
+        <v>-1.3432</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.354</v>
+        <v>-1.2484</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3992</v>
+        <v>-0.4904</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9548</v>
+        <v>-0.7581</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4141</v>
+        <v>0.8545</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5027</v>
+        <v>0.285</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0886</v>
+        <v>0.5695</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4565</v>
+        <v>1.9053</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4071</v>
+        <v>2.2198</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8636</v>
+        <v>-0.3145</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2731</v>
+        <v>3.1492</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1141</v>
+        <v>2.2785</v>
       </c>
       <c r="L19" t="n">
-        <v>2.159</v>
+        <v>0.8707</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8166</v>
+        <v>-1.2439</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5212</v>
+        <v>-0.0587</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2954</v>
+        <v>-1.1852</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4952</v>
+        <v>-4.5526</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0919</v>
+        <v>-1.1112</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1785</v>
+        <v>-0.6483</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2704</v>
+        <v>-0.4629</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2763</v>
+        <v>2.3367</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2881</v>
+        <v>0.3092</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2277</v>
+        <v>0.2358</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0604</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9056</v>
+        <v>0.4609</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2149</v>
+        <v>-0.3969</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3092</v>
+        <v>0.8578</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1835</v>
+        <v>2.2511</v>
       </c>
       <c r="K20" t="n">
-        <v>2.296</v>
+        <v>0.1067</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8875</v>
+        <v>2.1444</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2779</v>
+        <v>-1.7902</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.5036</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1967</v>
+        <v>-1.2866</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.5367</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6952</v>
+        <v>-0.202</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7652</v>
+        <v>-0.0561</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.93</v>
+        <v>-0.146</v>
       </c>
       <c r="V20" t="n">
-        <v>2.3461</v>
+        <v>0.278</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3461</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4175</v>
+        <v>-0.7177</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0831</v>
+        <v>-1.2079</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5006</v>
+        <v>0.4901</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2441</v>
+        <v>0.3159</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1326</v>
+        <v>0.3159</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1115</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2475</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6856</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5619</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0034</v>
+        <v>0.3159</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.553</v>
+        <v>0.3159</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4504</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3135</v>
+        <v>-0.1231</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3308</v>
+        <v>-0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0173</v>
+        <v>-0.0534</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2946</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7779</v>
+        <v>-0.964</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2037</v>
+        <v>0.0048</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4258</v>
+        <v>-0.9687</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3145</v>
+        <v>-0.3123</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3145</v>
+        <v>-0.1724</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3145</v>
+        <v>-0.3868</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3145</v>
+        <v>-0.1724</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1851</v>
+        <v>-0.0174</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1155</v>
+        <v>0.0523</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0021</v>
+        <v>-1.2072</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0051</v>
+        <v>0.347</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0072</v>
+        <v>-1.5542</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3144</v>
+        <v>1.2512</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1732</v>
+        <v>0.143</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1413</v>
+        <v>1.1081</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0746</v>
+        <v>2.2241</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.6755</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0746</v>
+        <v>1.5486</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3891</v>
+        <v>-0.9729</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1732</v>
+        <v>-0.5325</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2159</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0487</v>
+        <v>0.5124</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0696</v>
+        <v>0.6268</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0209</v>
+        <v>-0.1144</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-2.2879</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.526</v>
+        <v>-1.4234</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9502</v>
+        <v>-0.8387</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5758</v>
+        <v>-0.5847</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3509</v>
+        <v>0.3588</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0463</v>
+        <v>-0.0405</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3972</v>
+        <v>0.3993</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6875</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3381</v>
+        <v>-0.3287</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3536</v>
+        <v>-0.2682</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.1078</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5234</v>
+        <v>-1.5139</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5234</v>
+        <v>-1.5139</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.249499999999998</v>
+        <v>10.828</v>
       </c>
       <c r="E25" t="n">
-        <v>13.9528</v>
+        <v>13.6538</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.703399999999999</v>
+        <v>-2.8256</v>
       </c>
       <c r="G25" t="n">
-        <v>17.4362</v>
+        <v>17.4759</v>
       </c>
       <c r="H25" t="n">
-        <v>3.295800000000001</v>
+        <v>3.3705</v>
       </c>
       <c r="I25" t="n">
-        <v>14.1403</v>
+        <v>14.1052</v>
       </c>
       <c r="J25" t="n">
-        <v>27.3275</v>
+        <v>27.1347</v>
       </c>
       <c r="K25" t="n">
-        <v>5.830899999999999</v>
+        <v>5.748499999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>21.4966</v>
+        <v>21.3861</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.891300000000001</v>
+        <v>-9.658899999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.5351</v>
+        <v>-2.378099999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.3563</v>
+        <v>-7.280900000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.6708</v>
+        <v>-5.690699999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-22.6834</v>
+        <v>-22.7631</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.990300000000001</v>
+        <v>-3.4363</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8467</v>
+        <v>-0.8384999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.1435</v>
+        <v>-2.5979</v>
       </c>
       <c r="V25" t="n">
-        <v>2.4743</v>
+        <v>2.4796</v>
       </c>
       <c r="W25" t="n">
-        <v>10.1554</v>
+        <v>10.1207</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.681099999999999</v>
+        <v>-7.6412</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104625_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104625_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.1207</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.9692</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.5139</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104625_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.6412</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
